--- a/research/traditional_assets/database/data/netherlands/netherlands_software_internet.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_internet.xlsx
@@ -588,118 +588,109 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0583</v>
-      </c>
-      <c r="E2">
-        <v>0.728</v>
+        <v>-0.0528</v>
       </c>
       <c r="G2">
-        <v>0.1616860465116279</v>
+        <v>-0.03758865248226949</v>
       </c>
       <c r="H2">
-        <v>-0.009825581395348839</v>
+        <v>-0.2177304964539007</v>
       </c>
       <c r="I2">
-        <v>-0.0138953488372093</v>
+        <v>-0.2205673758865248</v>
       </c>
       <c r="J2">
-        <v>-0.0138953488372093</v>
+        <v>-0.2205673758865248</v>
       </c>
       <c r="K2">
-        <v>0.732</v>
+        <v>-1.64</v>
       </c>
       <c r="L2">
-        <v>0.04255813953488372</v>
+        <v>-0.1163120567375887</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.009534883720930233</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.328</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.009534883720930233</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>11.5</v>
+        <v>9.41</v>
       </c>
       <c r="V2">
-        <v>0.2839506172839506</v>
+        <v>0.273546511627907</v>
       </c>
       <c r="W2">
-        <v>0.06256410256410257</v>
+        <v>-0.1261538461538461</v>
       </c>
       <c r="X2">
-        <v>0.06017211410837678</v>
+        <v>0.1143585489131695</v>
       </c>
       <c r="Y2">
-        <v>0.002391988455725788</v>
-      </c>
-      <c r="Z2">
-        <v>5.165165165165167</v>
-      </c>
-      <c r="AA2">
-        <v>-0.0717717717717718</v>
+        <v>-0.2405123950670156</v>
       </c>
       <c r="AB2">
-        <v>0.05925777714886802</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1310295489206398</v>
+        <v>0.1134234397902887</v>
       </c>
       <c r="AD2">
-        <v>0.887</v>
+        <v>0.443</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.887</v>
+        <v>0.443</v>
       </c>
       <c r="AG2">
-        <v>-10.613</v>
+        <v>-8.967000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.02143185058110035</v>
+        <v>0.01271417501363258</v>
       </c>
       <c r="AI2">
-        <v>0.06387268668538922</v>
+        <v>0.03975590056537737</v>
       </c>
       <c r="AJ2">
-        <v>-0.355104225917623</v>
+        <v>-0.3525734282231746</v>
       </c>
       <c r="AK2">
-        <v>-4.446166736489316</v>
+        <v>-5.174264281592618</v>
       </c>
       <c r="AL2">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>-0.188</v>
+        <v>0.036</v>
       </c>
       <c r="AN2">
-        <v>-5.248520710059172</v>
+        <v>-0.144299674267101</v>
       </c>
       <c r="AO2">
-        <v>-5.195652173913043</v>
+        <v>-86.38888888888889</v>
       </c>
       <c r="AP2">
-        <v>62.79881656804733</v>
+        <v>2.92084690553746</v>
       </c>
       <c r="AQ2">
-        <v>1.271276595744681</v>
+        <v>-86.38888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +710,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0583</v>
-      </c>
-      <c r="E3">
-        <v>0.728</v>
+        <v>-0.0528</v>
       </c>
       <c r="G3">
-        <v>0.1616860465116279</v>
+        <v>-0.03758865248226949</v>
       </c>
       <c r="H3">
-        <v>-0.009825581395348839</v>
+        <v>-0.2177304964539007</v>
       </c>
       <c r="I3">
-        <v>-0.0138953488372093</v>
+        <v>-0.2205673758865248</v>
       </c>
       <c r="J3">
-        <v>-0.0138953488372093</v>
+        <v>-0.2205673758865248</v>
       </c>
       <c r="K3">
-        <v>0.732</v>
+        <v>-1.64</v>
       </c>
       <c r="L3">
-        <v>0.04255813953488372</v>
+        <v>-0.1163120567375887</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.328</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.009534883720930233</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.328</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.009534883720930233</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>11.5</v>
+        <v>9.41</v>
       </c>
       <c r="V3">
-        <v>0.2839506172839506</v>
+        <v>0.273546511627907</v>
       </c>
       <c r="W3">
-        <v>0.06256410256410257</v>
+        <v>-0.1261538461538461</v>
       </c>
       <c r="X3">
-        <v>0.06017211410837678</v>
+        <v>0.1143585489131695</v>
       </c>
       <c r="Y3">
-        <v>0.002391988455725788</v>
-      </c>
-      <c r="Z3">
-        <v>5.165165165165167</v>
-      </c>
-      <c r="AA3">
-        <v>-0.0717717717717718</v>
+        <v>-0.2405123950670156</v>
       </c>
       <c r="AB3">
-        <v>0.05925777714886802</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1310295489206398</v>
+        <v>0.1134234397902887</v>
       </c>
       <c r="AD3">
-        <v>0.887</v>
+        <v>0.443</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.887</v>
+        <v>0.443</v>
       </c>
       <c r="AG3">
-        <v>-10.613</v>
+        <v>-8.967000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.02143185058110035</v>
+        <v>0.01271417501363258</v>
       </c>
       <c r="AI3">
-        <v>0.06387268668538922</v>
+        <v>0.03975590056537737</v>
       </c>
       <c r="AJ3">
-        <v>-0.355104225917623</v>
+        <v>-0.3525734282231746</v>
       </c>
       <c r="AK3">
-        <v>-4.446166736489316</v>
+        <v>-5.174264281592618</v>
       </c>
       <c r="AL3">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="AM3">
-        <v>-0.188</v>
+        <v>0.036</v>
       </c>
       <c r="AN3">
-        <v>-5.248520710059172</v>
+        <v>-0.144299674267101</v>
       </c>
       <c r="AO3">
-        <v>-5.195652173913043</v>
+        <v>-86.38888888888889</v>
       </c>
       <c r="AP3">
-        <v>62.79881656804733</v>
+        <v>2.92084690553746</v>
       </c>
       <c r="AQ3">
-        <v>1.271276595744681</v>
+        <v>-86.38888888888889</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_software_internet.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_software_internet.xlsx
@@ -587,44 +587,29 @@
           <t>Software (Internet)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.0528</v>
-      </c>
-      <c r="G2">
-        <v>-0.03758865248226949</v>
-      </c>
-      <c r="H2">
-        <v>-0.2177304964539007</v>
-      </c>
-      <c r="I2">
-        <v>-0.2205673758865248</v>
-      </c>
-      <c r="J2">
-        <v>-0.2205673758865248</v>
+      <c r="E2">
+        <v>2.134</v>
       </c>
       <c r="K2">
-        <v>-1.64</v>
-      </c>
-      <c r="L2">
-        <v>-0.1163120567375887</v>
+        <v>58.9</v>
       </c>
       <c r="M2">
-        <v>0.328</v>
+        <v>6.2</v>
       </c>
       <c r="N2">
-        <v>0.009534883720930233</v>
+        <v>1.980830670926518</v>
       </c>
       <c r="O2">
-        <v>-0.2</v>
+        <v>0.1052631578947369</v>
       </c>
       <c r="P2">
-        <v>0.328</v>
+        <v>6.2</v>
       </c>
       <c r="Q2">
-        <v>0.009534883720930233</v>
+        <v>1.980830670926518</v>
       </c>
       <c r="R2">
-        <v>-0.2</v>
+        <v>0.1052631578947369</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,64 +618,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.41</v>
+        <v>0.55</v>
       </c>
       <c r="V2">
-        <v>0.273546511627907</v>
+        <v>0.1757188498402556</v>
       </c>
       <c r="W2">
-        <v>-0.1261538461538461</v>
+        <v>5.504672897196262</v>
       </c>
       <c r="X2">
-        <v>0.1143585489131695</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="Y2">
-        <v>-0.2405123950670156</v>
+        <v>5.407687117960179</v>
       </c>
       <c r="AB2">
-        <v>0.1134234397902887</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="AD2">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-8.967000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="AH2">
-        <v>0.01271417501363258</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.03975590056537737</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.3525734282231746</v>
+        <v>-0.2131782945736434</v>
       </c>
       <c r="AK2">
-        <v>-5.174264281592618</v>
+        <v>-0.1470588235294118</v>
       </c>
       <c r="AL2">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="AN2">
-        <v>-0.144299674267101</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-86.38888888888889</v>
+        <v>-2830</v>
       </c>
       <c r="AP2">
-        <v>2.92084690553746</v>
+        <v>0.09821428571428573</v>
       </c>
       <c r="AQ2">
-        <v>-86.38888888888889</v>
+        <v>-2830</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +686,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TIE Kinetix N.V. (ENXTAM:TIE)</t>
+          <t>Titan N.V. (ENXTAM:TITAN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,44 +694,29 @@
           <t>Software (Internet)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0528</v>
-      </c>
-      <c r="G3">
-        <v>-0.03758865248226949</v>
-      </c>
-      <c r="H3">
-        <v>-0.2177304964539007</v>
-      </c>
-      <c r="I3">
-        <v>-0.2205673758865248</v>
-      </c>
-      <c r="J3">
-        <v>-0.2205673758865248</v>
+      <c r="E3">
+        <v>2.134</v>
       </c>
       <c r="K3">
-        <v>-1.64</v>
-      </c>
-      <c r="L3">
-        <v>-0.1163120567375887</v>
+        <v>58.9</v>
       </c>
       <c r="M3">
-        <v>0.328</v>
+        <v>6.2</v>
       </c>
       <c r="N3">
-        <v>0.009534883720930233</v>
+        <v>1.980830670926518</v>
       </c>
       <c r="O3">
-        <v>-0.2</v>
+        <v>0.1052631578947369</v>
       </c>
       <c r="P3">
-        <v>0.328</v>
+        <v>6.2</v>
       </c>
       <c r="Q3">
-        <v>0.009534883720930233</v>
+        <v>1.980830670926518</v>
       </c>
       <c r="R3">
-        <v>-0.2</v>
+        <v>0.1052631578947369</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,64 +725,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.41</v>
+        <v>0.55</v>
       </c>
       <c r="V3">
-        <v>0.273546511627907</v>
+        <v>0.1757188498402556</v>
       </c>
       <c r="W3">
-        <v>-0.1261538461538461</v>
+        <v>5.504672897196262</v>
       </c>
       <c r="X3">
-        <v>0.1143585489131695</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="Y3">
-        <v>-0.2405123950670156</v>
+        <v>5.407687117960179</v>
       </c>
       <c r="AB3">
-        <v>0.1134234397902887</v>
+        <v>0.09698577923608293</v>
       </c>
       <c r="AD3">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-8.967000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="AH3">
-        <v>0.01271417501363258</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.03975590056537737</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3525734282231746</v>
+        <v>-0.2131782945736434</v>
       </c>
       <c r="AK3">
-        <v>-5.174264281592618</v>
+        <v>-0.1470588235294118</v>
       </c>
       <c r="AL3">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0.036</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
-        <v>-0.144299674267101</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-86.38888888888889</v>
+        <v>-2830</v>
       </c>
       <c r="AP3">
-        <v>2.92084690553746</v>
+        <v>0.09821428571428573</v>
       </c>
       <c r="AQ3">
-        <v>-86.38888888888889</v>
+        <v>-2830</v>
       </c>
     </row>
   </sheetData>
